--- a/49954_Cuenca_Perene/_raw_reportes_xlsx/IDConfig_64967_completo.xlsx
+++ b/49954_Cuenca_Perene/_raw_reportes_xlsx/IDConfig_64967_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rd363b2cdd6804984"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R00d569dc7c364e09"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,141 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     72.9292</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     57.1025</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     55.1908</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     59.2023</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     61.1133</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     80.3562</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     50.0589</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     42.7445</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     48.1747</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>14/08/2026</x:t>
         </x:is>
       </x:c>

--- a/49954_Cuenca_Perene/_raw_reportes_xlsx/IDConfig_64967_completo.xlsx
+++ b/49954_Cuenca_Perene/_raw_reportes_xlsx/IDConfig_64967_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R00d569dc7c364e09"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R36d4b27b4a094215"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,726 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     42.9321</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     38.0680</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     27.6620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     43.3249</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     22.8509</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     32.1622</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     41.6470</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     34.8509</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     38.1579</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     52.0682</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     45.6586</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     54.1326</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     62.3867</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     77.9597</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     35.5348</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     46.5288</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     37.1035</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     49.6702</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     50.6576</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     40.8837</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     67.0720</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     76.6057</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     75.5632</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    103.1325</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     80.2485</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     60.9960</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     36.4052</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     39.6378</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     69.4812</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     52.1854</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     52.1862</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     56.0797</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     40.0961</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     37.0673</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     35.1202</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     33.8799</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     29.3917</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     36.0706</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     34.8509</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     30.8970</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     45.5413</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     36.1360</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     41.7683</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     48.2951</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     50.3595</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     62.3867</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     58.1442</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>     60.5467</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>23/08/2026</x:t>
         </x:is>
       </x:c>
